--- a/xlsx/单位/英雄.xlsx
+++ b/xlsx/单位/英雄.xlsx
@@ -1419,7 +1419,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2778,7 +2778,6 @@
       <c r="Q3" t="s">
         <v>188</v>
       </c>
-      <c r="R3"/>
       <c r="U3">
         <v>5</v>
       </c>
@@ -2829,7 +2828,6 @@
       <c r="Q4" t="s">
         <v>196</v>
       </c>
-      <c r="R4"/>
       <c r="V4">
         <v>40</v>
       </c>
@@ -2880,7 +2878,6 @@
       <c r="Q5" t="s">
         <v>204</v>
       </c>
-      <c r="R5"/>
       <c r="V5">
         <v>40</v>
       </c>
@@ -2919,7 +2916,6 @@
       <c r="Q6" t="s">
         <v>209</v>
       </c>
-      <c r="R6"/>
       <c r="T6">
         <v>360</v>
       </c>
@@ -2985,7 +2981,6 @@
       <c r="Q7" t="s">
         <v>222</v>
       </c>
-      <c r="R7"/>
       <c r="T7">
         <v>320</v>
       </c>
@@ -3194,7 +3189,6 @@
       <c r="Q9" t="s">
         <v>251</v>
       </c>
-      <c r="R9"/>
       <c r="S9">
         <v>50</v>
       </c>
@@ -3368,7 +3362,6 @@
       <c r="Q10" t="s">
         <v>274</v>
       </c>
-      <c r="R10"/>
       <c r="T10">
         <v>300</v>
       </c>
@@ -3571,7 +3564,6 @@
       <c r="Q13" t="s">
         <v>292</v>
       </c>
-      <c r="R13"/>
       <c r="S13">
         <v>50</v>
       </c>

--- a/xlsx/单位/英雄.xlsx
+++ b/xlsx/单位/英雄.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="297">
   <si>
     <t>id</t>
   </si>
@@ -593,7 +593,7 @@
     <t>TALT</t>
   </si>
   <si>
-    <t>Ault,AInv</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>stand</t>
@@ -617,9 +617,6 @@
     <t>2.25</t>
   </si>
   <si>
-    <t>Adtg,AInv,Ault</t>
-  </si>
-  <si>
     <t>0.1</t>
   </si>
   <si>
@@ -641,9 +638,6 @@
     <t>Ewar</t>
   </si>
   <si>
-    <t>A0DB,AInv,Ault</t>
-  </si>
-  <si>
     <t>Remg,Rema,Reuv</t>
   </si>
   <si>
@@ -656,9 +650,6 @@
     <t>1.5</t>
   </si>
   <si>
-    <t>A044,AInv,Ault</t>
-  </si>
-  <si>
     <t>2.0</t>
   </si>
   <si>
@@ -695,9 +686,6 @@
     <t>nnsa,nnad</t>
   </si>
   <si>
-    <t>A09V,AInv</t>
-  </si>
-  <si>
     <t>ground,ward,structure,debris,item</t>
   </si>
   <si>
@@ -782,9 +770,6 @@
     <t>Units\Critters\Marine\Marine.mdl</t>
   </si>
   <si>
-    <t>A09X,A09P</t>
-  </si>
-  <si>
     <t>ground,ward,structure,tree,debris,item,air</t>
   </si>
   <si>
@@ -806,9 +791,6 @@
     <t>0.17</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>0.7</t>
   </si>
   <si>
@@ -851,9 +833,6 @@
     <t>ReplaceableTextures\CommandButtons\BTNAvatar.blp</t>
   </si>
   <si>
-    <t>Apg2,AInv</t>
-  </si>
-  <si>
     <t>alternate</t>
   </si>
   <si>
@@ -875,9 +854,6 @@
     <t>娜迦女海巫(|cffffcc00N|r)</t>
   </si>
   <si>
-    <t>A01B,A09V,AInv</t>
-  </si>
-  <si>
     <t>pierce</t>
   </si>
   <si>
@@ -903,9 +879,6 @@
   </si>
   <si>
     <t>units\demon\HeroChaosBladeMaster\HeroChaosBladeMaster.mdl</t>
-  </si>
-  <si>
-    <t>AInv,A0PD</t>
   </si>
   <si>
     <t>chaos</t>
@@ -2775,7 +2748,7 @@
       <c r="P3">
         <v>3</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>188</v>
       </c>
       <c r="U3">
@@ -2825,8 +2798,8 @@
       <c r="J4" t="s">
         <v>195</v>
       </c>
-      <c r="Q4" t="s">
-        <v>196</v>
+      <c r="R4" t="s">
+        <v>188</v>
       </c>
       <c r="V4">
         <v>40</v>
@@ -2835,13 +2808,13 @@
         <v>100</v>
       </c>
       <c r="BE4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BF4">
         <v>1100</v>
       </c>
       <c r="BM4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BQ4">
         <v>1000</v>
@@ -2850,16 +2823,16 @@
         <v>1000</v>
       </c>
       <c r="BX4" t="s">
+        <v>198</v>
+      </c>
+      <c r="CB4" t="s">
         <v>199</v>
       </c>
-      <c r="CB4" t="s">
+      <c r="CE4" t="s">
         <v>200</v>
       </c>
-      <c r="CE4" t="s">
+      <c r="CF4" t="s">
         <v>201</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>202</v>
       </c>
       <c r="CJ4" t="s">
         <v>195</v>
@@ -2867,16 +2840,16 @@
     </row>
     <row r="5" spans="1:89">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I5" t="s">
         <v>186</v>
       </c>
-      <c r="Q5" t="s">
-        <v>204</v>
+      <c r="R5" t="s">
+        <v>188</v>
       </c>
       <c r="V5">
         <v>40</v>
@@ -2885,36 +2858,36 @@
         <v>100</v>
       </c>
       <c r="BM5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="CB5" t="s">
+        <v>199</v>
+      </c>
+      <c r="CE5" t="s">
         <v>200</v>
       </c>
-      <c r="CE5" t="s">
+      <c r="CF5" t="s">
         <v>201</v>
       </c>
-      <c r="CF5" t="s">
-        <v>202</v>
-      </c>
       <c r="CK5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I6" t="s">
         <v>186</v>
       </c>
       <c r="J6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>209</v>
+        <v>206</v>
+      </c>
+      <c r="R6" t="s">
+        <v>188</v>
       </c>
       <c r="T6">
         <v>360</v>
@@ -2926,39 +2899,39 @@
         <v>100</v>
       </c>
       <c r="AL6" t="s">
+        <v>207</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>208</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>209</v>
+      </c>
+      <c r="CB6" t="s">
         <v>210</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>211</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>205</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>212</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:93">
       <c r="A7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" t="s">
         <v>214</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" t="s">
         <v>215</v>
-      </c>
-      <c r="C7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D7" t="s">
-        <v>217</v>
-      </c>
-      <c r="E7" t="s">
-        <v>217</v>
-      </c>
-      <c r="H7" t="s">
-        <v>218</v>
       </c>
       <c r="I7" t="s">
         <v>190</v>
@@ -2970,16 +2943,16 @@
         <v>400</v>
       </c>
       <c r="M7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O7" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>222</v>
+        <v>218</v>
+      </c>
+      <c r="R7" t="s">
+        <v>188</v>
       </c>
       <c r="T7">
         <v>320</v>
@@ -2988,10 +2961,10 @@
         <v>5</v>
       </c>
       <c r="W7" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="X7" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AB7">
         <v>700</v>
@@ -3006,19 +2979,19 @@
         <v>16</v>
       </c>
       <c r="AK7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AL7" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AM7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AQ7" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AS7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AV7">
         <v>1</v>
@@ -3027,16 +3000,16 @@
         <v>1500</v>
       </c>
       <c r="AY7" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="BC7" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="BD7" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="BE7" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="BF7">
         <v>0</v>
@@ -3045,63 +3018,63 @@
         <v>2000</v>
       </c>
       <c r="BH7" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="BM7" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="BQ7">
         <v>200</v>
       </c>
       <c r="BS7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="BU7">
         <v>3</v>
       </c>
       <c r="BV7" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="BX7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="BZ7" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="CB7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="CC7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="CE7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="CF7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="CG7">
         <v>500</v>
       </c>
       <c r="CJ7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="CK7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="CO7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:87">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -3109,6 +3082,9 @@
       <c r="I8" t="s">
         <v>186</v>
       </c>
+      <c r="R8" t="s">
+        <v>188</v>
+      </c>
       <c r="S8">
         <v>30</v>
       </c>
@@ -3122,28 +3098,28 @@
         <v>100</v>
       </c>
       <c r="AD8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AK8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AQ8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AR8">
         <v>500</v>
       </c>
       <c r="BM8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="BN8" t="s">
         <v>186</v>
       </c>
       <c r="BV8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="BZ8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="CB8" t="s">
         <v>186</v>
@@ -3154,31 +3130,31 @@
     </row>
     <row r="9" spans="1:90">
       <c r="A9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" t="s">
         <v>243</v>
-      </c>
-      <c r="B9" t="s">
-        <v>244</v>
-      </c>
-      <c r="C9" t="s">
-        <v>245</v>
-      </c>
-      <c r="D9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E9" t="s">
-        <v>247</v>
       </c>
       <c r="H9" t="s">
         <v>190</v>
       </c>
       <c r="J9" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="M9" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N9" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="O9" t="s">
         <v>187</v>
@@ -3186,8 +3162,8 @@
       <c r="P9">
         <v>3</v>
       </c>
-      <c r="Q9" t="s">
-        <v>251</v>
+      <c r="R9" t="s">
+        <v>188</v>
       </c>
       <c r="S9">
         <v>50</v>
@@ -3199,13 +3175,13 @@
         <v>5</v>
       </c>
       <c r="W9" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="X9" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AA9" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AB9">
         <v>300</v>
@@ -3223,13 +3199,13 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AL9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AM9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AN9">
         <v>155</v>
@@ -3241,13 +3217,13 @@
         <v>55</v>
       </c>
       <c r="AQ9" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AR9">
         <v>1000</v>
       </c>
       <c r="AS9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AT9">
         <v>2</v>
@@ -3259,64 +3235,64 @@
         <v>1</v>
       </c>
       <c r="AY9" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AZ9">
         <v>180</v>
       </c>
       <c r="BB9" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BD9" t="s">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="BF9">
         <v>10000</v>
       </c>
       <c r="BJ9" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="BK9">
         <v>1</v>
       </c>
       <c r="BL9" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="BM9" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="BN9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="BO9" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="BP9" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="BQ9">
         <v>600</v>
       </c>
       <c r="BS9" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BV9" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="BW9">
         <v>1</v>
       </c>
       <c r="BX9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="BZ9" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="CC9" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="CD9" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="CE9" t="s">
         <v>192</v>
@@ -3328,39 +3304,39 @@
         <v>1</v>
       </c>
       <c r="CL9" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:84">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B10" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C10" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E10" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G10">
         <v>300</v>
       </c>
       <c r="H10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I10" t="s">
         <v>190</v>
       </c>
       <c r="M10" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>274</v>
+        <v>267</v>
+      </c>
+      <c r="R10" t="s">
+        <v>188</v>
       </c>
       <c r="T10">
         <v>300</v>
@@ -3369,7 +3345,7 @@
         <v>40</v>
       </c>
       <c r="Z10" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AC10">
         <v>200</v>
@@ -3384,42 +3360,42 @@
         <v>24</v>
       </c>
       <c r="AM10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AQ10" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AS10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="BS10" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="BV10" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="BZ10" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="CC10" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="CE10" t="s">
+        <v>200</v>
+      </c>
+      <c r="CF10" t="s">
         <v>201</v>
-      </c>
-      <c r="CF10" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:84">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B11" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3428,11 +3404,14 @@
         <v>300</v>
       </c>
       <c r="H11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I11" t="s">
         <v>190</v>
       </c>
+      <c r="R11" t="s">
+        <v>188</v>
+      </c>
       <c r="T11">
         <v>300</v>
       </c>
@@ -3443,24 +3422,24 @@
         <v>80</v>
       </c>
       <c r="BM11" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="CE11" t="s">
+        <v>200</v>
+      </c>
+      <c r="CF11" t="s">
         <v>201</v>
-      </c>
-      <c r="CF11" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:89">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D12" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="K12">
         <v>600</v>
@@ -3468,10 +3447,9 @@
       <c r="L12">
         <v>400</v>
       </c>
-      <c r="Q12" t="s">
-        <v>282</v>
-      </c>
-      <c r="R12"/>
+      <c r="R12" t="s">
+        <v>188</v>
+      </c>
       <c r="T12">
         <v>320</v>
       </c>
@@ -3479,7 +3457,7 @@
         <v>5</v>
       </c>
       <c r="Y12" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="AB12">
         <v>500</v>
@@ -3494,7 +3472,7 @@
         <v>1500</v>
       </c>
       <c r="BE12" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="BF12">
         <v>2000</v>
@@ -3503,7 +3481,7 @@
         <v>3</v>
       </c>
       <c r="BM12" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="BQ12">
         <v>900</v>
@@ -3512,39 +3490,39 @@
         <v>1000</v>
       </c>
       <c r="BX12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CB12" t="s">
         <v>186</v>
       </c>
       <c r="CE12" t="s">
+        <v>200</v>
+      </c>
+      <c r="CF12" t="s">
         <v>201</v>
-      </c>
-      <c r="CF12" t="s">
-        <v>202</v>
       </c>
       <c r="CG12">
         <v>500</v>
       </c>
       <c r="CK12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:92">
       <c r="A13" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B13" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C13" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E13" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="I13" t="s">
         <v>186</v>
@@ -3556,13 +3534,13 @@
         <v>200</v>
       </c>
       <c r="M13" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="N13" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>292</v>
+        <v>283</v>
+      </c>
+      <c r="R13" t="s">
+        <v>188</v>
       </c>
       <c r="S13">
         <v>50</v>
@@ -3574,16 +3552,16 @@
         <v>40</v>
       </c>
       <c r="Y13" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="AC13">
         <v>90</v>
       </c>
       <c r="AE13" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AF13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG13" t="s">
         <v>126</v>
@@ -3601,64 +3579,64 @@
         <v>195</v>
       </c>
       <c r="AL13" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AM13" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AQ13" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AZ13">
         <v>180</v>
       </c>
       <c r="BA13" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="BI13" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="BK13">
         <v>3</v>
       </c>
       <c r="BM13" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="BS13" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="BT13" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="BV13" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="BY13" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BZ13" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="CA13">
         <v>1</v>
       </c>
       <c r="CB13" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="CC13" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="CD13" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="CH13" t="s">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="CI13">
         <v>10</v>
       </c>
       <c r="CN13" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
